--- a/Assets/GameResource/Excel/怪物配置.xlsx
+++ b/Assets/GameResource/Excel/怪物配置.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD638D3-0FAD-40CC-9FA3-B5730E57132A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100FF229-BF5A-4C5C-97B0-B662A1BDE0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,9 +35,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
-    <t>Chapters</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>法术伤害减免系数</t>
-  </si>
-  <si>
     <t>是否是Boss</t>
   </si>
   <si>
@@ -101,10 +95,6 @@
     <t>哥布林之王</t>
   </si>
   <si>
-    <t>地图id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>预制体寻址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -113,10 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>物理伤害减免系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -129,31 +115,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>敌人描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>敌人id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>敌人初始攻击力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人成长攻击力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人初始生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人成长生命值</t>
+    <t>DungeonId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地牢id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物抗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法抗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成长生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成长攻击力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始攻击力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -517,116 +519,116 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="I3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -637,10 +639,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2">
         <v>3</v>
@@ -665,10 +667,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2">
         <v>6</v>
@@ -693,10 +695,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2">
         <v>8</v>
@@ -723,10 +725,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
@@ -753,10 +755,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2">
         <v>10</v>

--- a/Assets/GameResource/Excel/怪物配置.xlsx
+++ b/Assets/GameResource/Excel/怪物配置.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100FF229-BF5A-4C5C-97B0-B662A1BDE0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E473ED55-44A8-4AD5-A168-434B114C4C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Name</t>
   </si>
@@ -156,6 +156,14 @@
   </si>
   <si>
     <t>名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionSpeed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -210,22 +218,22 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,98 +510,106 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.44140625" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
     <col min="4" max="4" width="14.109375" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="9" width="14.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="23.77734375" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.88671875" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="5" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>25</v>
       </c>
@@ -624,74 +640,83 @@
       <c r="J3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>9001</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>3</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>25</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>4</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>9002</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>6</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>15</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>2</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>9003</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -700,28 +725,31 @@
       <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>8</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>2</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>40</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>5</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="1">
         <v>20</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>9004</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -730,28 +758,31 @@
       <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>5</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>2</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>60</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>6</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="1">
         <v>20</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>9005</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -760,10 +791,10 @@
       <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>10</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8">
@@ -772,13 +803,16 @@
       <c r="H8">
         <v>10</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <v>20</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>30</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
+        <v>5</v>
+      </c>
+      <c r="L8">
         <v>1</v>
       </c>
     </row>

--- a/Assets/GameResource/Excel/怪物配置.xlsx
+++ b/Assets/GameResource/Excel/怪物配置.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E473ED55-44A8-4AD5-A168-434B114C4C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E5CE20-8023-42A9-A46F-02828C057D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>Name</t>
   </si>
@@ -56,9 +56,6 @@
     <t>IsBoss</t>
   </si>
   <si>
-    <t>ResAddress</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -95,10 +92,6 @@
     <t>哥布林之王</t>
   </si>
   <si>
-    <t>预制体寻址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PhyDef</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -165,6 +158,29 @@
   <si>
     <t>ActionSpeed</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconAdd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片寻址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亡灵敌人</t>
+  </si>
+  <si>
+    <t>恶魔敌人</t>
+  </si>
+  <si>
+    <t>法师敌人</t>
+  </si>
+  <si>
+    <t>狼人敌人</t>
+  </si>
+  <si>
+    <t>鬼灵敌人</t>
   </si>
 </sst>
 </file>
@@ -215,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -234,6 +250,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,16 +548,16 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -553,101 +572,101 @@
         <v>4</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>7</v>
+      <c r="M1" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="5" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="L3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -658,10 +677,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E4" s="1">
         <v>3</v>
@@ -680,6 +699,9 @@
       <c r="K4" s="1">
         <v>4</v>
       </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -689,10 +711,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="1">
         <v>6</v>
@@ -711,6 +733,9 @@
       <c r="K5" s="1">
         <v>4</v>
       </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -720,10 +745,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
       </c>
       <c r="E6" s="1">
         <v>8</v>
@@ -743,6 +768,9 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1">
         <v>5</v>
+      </c>
+      <c r="M6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -753,10 +781,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -776,6 +804,9 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1">
         <v>5</v>
+      </c>
+      <c r="M7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -786,10 +817,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1">
         <v>10</v>
@@ -814,6 +845,9 @@
       </c>
       <c r="L8">
         <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
